--- a/app/config/assets/framework/forms/framework/framework.xlsx
+++ b/app/config/assets/framework/forms/framework/framework.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clarice\odk-reference\app-designer\app\config\assets\framework\forms\framework\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\assets\framework\forms\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59CDE5E-6B96-4B2E-9BBB-45C3C8C0287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="5" r:id="rId1"/>
@@ -19,7 +20,7 @@
     <sheet name="framework_translations" sheetId="9" r:id="rId5"/>
     <sheet name="common_translations" sheetId="10" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="140001" concurrentCalc="0"/>
+  <calcPr calcId="140001"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="244">
   <si>
     <t>comments</t>
   </si>
@@ -509,15 +510,6 @@
   </si>
   <si>
     <t>display.title.text</t>
-  </si>
-  <si>
-    <t>form_id_here</t>
-  </si>
-  <si>
-    <t>form_title_here</t>
-  </si>
-  <si>
-    <t>'?' + odkSurvey.getHashString('form_id_here')</t>
   </si>
   <si>
     <t>display.title.text.en</t>
@@ -770,11 +762,38 @@
   <si>
     <t>text.en</t>
   </si>
+  <si>
+    <t>consulta</t>
+  </si>
+  <si>
+    <t>Criacão de Postos Sentinelas para seguimento do paludismo e outras doencas</t>
+  </si>
+  <si>
+    <t>Introducao dos resultados de laboratorios</t>
+  </si>
+  <si>
+    <t>sentinela</t>
+  </si>
+  <si>
+    <t>Registro de consultas</t>
+  </si>
+  <si>
+    <t>resultado</t>
+  </si>
+  <si>
+    <t>"?" + odkSurvey.getHashString('sentinela')</t>
+  </si>
+  <si>
+    <t>"?" + odkSurvey.getHashString('sentinela','resultado')</t>
+  </si>
+  <si>
+    <t>"?" + odkSurvey.getHashString('sentinela','consulta')</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -917,7 +936,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -941,6 +960,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,7 +1115,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1126,9 +1148,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1161,6 +1200,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1336,7 +1392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1368,8 +1424,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="101.140625" customWidth="1"/>
@@ -1455,28 +1511,66 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" t="s">
+    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s">
+    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1492,8 +1586,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -1517,10 +1611,32 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -1535,7 +1651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1551,22 +1667,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I1" t="s">
         <v>0</v>
@@ -1628,7 +1744,7 @@
         <v>46</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
@@ -1640,27 +1756,27 @@
     <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
         <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F8" t="s">
         <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H8" t="s">
         <v>48</v>
@@ -1668,16 +1784,16 @@
     </row>
     <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1755,7 +1871,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1774,10 +1890,10 @@
         <v>59</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1788,7 +1904,7 @@
         <v>52</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1799,7 +1915,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1810,7 +1926,7 @@
         <v>54</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1821,7 +1937,7 @@
         <v>55</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1832,7 +1948,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -1846,7 +1962,7 @@
         <v>38</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1860,7 +1976,7 @@
         <v>149</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1874,7 +1990,7 @@
         <v>148</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -1888,7 +2004,7 @@
         <v>150</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1899,7 +2015,7 @@
         <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1910,7 +2026,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -1921,7 +2037,7 @@
         <v>62</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1932,7 +2048,7 @@
         <v>64</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -1943,7 +2059,7 @@
         <v>65</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1954,7 +2070,7 @@
         <v>66</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -1965,7 +2081,7 @@
         <v>67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1976,7 +2092,7 @@
         <v>73</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -1987,7 +2103,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1998,7 +2114,7 @@
         <v>77</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -2009,7 +2125,7 @@
         <v>79</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -2020,7 +2136,7 @@
         <v>81</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -2031,7 +2147,7 @@
         <v>83</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -2042,7 +2158,7 @@
         <v>85</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -2064,7 +2180,7 @@
         <v>89</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -2075,7 +2191,7 @@
         <v>94</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2086,7 +2202,7 @@
         <v>97</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2097,7 +2213,7 @@
         <v>96</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -2108,7 +2224,7 @@
         <v>100</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2119,7 +2235,7 @@
         <v>102</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -2130,7 +2246,7 @@
         <v>106</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -2141,7 +2257,7 @@
         <v>105</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -2152,7 +2268,7 @@
         <v>108</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="178.5" x14ac:dyDescent="0.2">
@@ -2163,7 +2279,7 @@
         <v>111</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2174,7 +2290,7 @@
         <v>113</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2185,7 +2301,7 @@
         <v>114</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2196,7 +2312,7 @@
         <v>117</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2207,7 +2323,7 @@
         <v>119</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2218,7 +2334,7 @@
         <v>121</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2229,7 +2345,7 @@
         <v>123</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2240,7 +2356,7 @@
         <v>125</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -2251,7 +2367,7 @@
         <v>127</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -2265,7 +2381,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -2276,7 +2392,7 @@
         <v>146</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2287,7 +2403,7 @@
         <v>132</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2298,7 +2414,7 @@
         <v>134</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2309,7 +2425,7 @@
         <v>136</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2320,7 +2436,7 @@
         <v>138</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2331,7 +2447,7 @@
         <v>139</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2342,7 +2458,7 @@
         <v>102</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2353,7 +2469,7 @@
         <v>140</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -2364,7 +2480,7 @@
         <v>132</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -2375,7 +2491,7 @@
         <v>147</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -2386,7 +2502,7 @@
         <v>152</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -2397,40 +2513,40 @@
         <v>153</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2440,7 +2556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2456,13 +2572,13 @@
         <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E1" t="s">
         <v>59</v>

--- a/app/config/assets/framework/forms/framework/framework.xlsx
+++ b/app/config/assets/framework/forms/framework/framework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\assets\framework\forms\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59CDE5E-6B96-4B2E-9BBB-45C3C8C0287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4629417F-7122-4B82-B278-3A81A2C572C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="4545" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="5" r:id="rId1"/>
@@ -766,9 +766,6 @@
     <t>consulta</t>
   </si>
   <si>
-    <t>Criacão de Postos Sentinelas para seguimento do paludismo e outras doencas</t>
-  </si>
-  <si>
     <t>Introducao dos resultados de laboratorios</t>
   </si>
   <si>
@@ -788,6 +785,9 @@
   </si>
   <si>
     <t>"?" + odkSurvey.getHashString('sentinela','consulta')</t>
+  </si>
+  <si>
+    <t>Criacao de Postos Sentinelas para seguimento do paludismo e outras doencas</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="101.140625" customWidth="1"/>
@@ -1511,66 +1511,66 @@
         <v>27</v>
       </c>
     </row>
+    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>235</v>
+      </c>
+    </row>
     <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>235</v>
+      <c r="B9" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
+    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
+    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
         <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
@@ -1622,10 +1622,10 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
@@ -1633,10 +1633,10 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/assets/framework/forms/framework/framework.xlsx
+++ b/app/config/assets/framework/forms/framework/framework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\assets\framework\forms\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4629417F-7122-4B82-B278-3A81A2C572C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0566E08F-92DA-4D96-84C2-B839032E8DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="4545" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="231">
   <si>
     <t>comments</t>
   </si>
@@ -146,15 +146,9 @@
     <t>Acknowledge</t>
   </si>
   <si>
-    <t>स्वीकार करना</t>
-  </si>
-  <si>
     <t>Deselect</t>
   </si>
   <si>
-    <t>अचयनित</t>
-  </si>
-  <si>
     <t>Back</t>
   </si>
   <si>
@@ -170,13 +164,7 @@
     <t>Required value was not provided.</t>
   </si>
   <si>
-    <t>सामान्य जावास्क्रिप्ट फ़्रेमवर्क</t>
-  </si>
-  <si>
     <t>English</t>
-  </si>
-  <si>
-    <t>Hindi</t>
   </si>
   <si>
     <t>constraint_message</t>
@@ -488,15 +476,6 @@
     <t>Scan Barcode</t>
   </si>
   <si>
-    <t>आगामी</t>
-  </si>
-  <si>
-    <t>लौटना</t>
-  </si>
-  <si>
-    <t>जारी रहना</t>
-  </si>
-  <si>
     <t>invalid_numeric_message</t>
   </si>
   <si>
@@ -521,28 +500,7 @@
     <t>en</t>
   </si>
   <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>display.title.text.hi</t>
-  </si>
-  <si>
-    <t>display.locale.text.hi</t>
-  </si>
-  <si>
-    <t>text.hi</t>
-  </si>
-  <si>
-    <t>हिंदी</t>
-  </si>
-  <si>
-    <t>अंग्रेज़ी</t>
-  </si>
-  <si>
     <t>Español</t>
-  </si>
-  <si>
-    <t xml:space="preserve">स्पेनिश </t>
   </si>
   <si>
     <t>Spanish</t>
@@ -789,12 +747,15 @@
   <si>
     <t>Criacao de Postos Sentinelas para seguimento do paludismo e outras doencas</t>
   </si>
+  <si>
+    <t>framework_variant</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -813,25 +774,24 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -936,7 +896,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -947,22 +907,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1457,10 +1420,10 @@
         <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1"/>
     </row>
@@ -1513,12 +1476,12 @@
     </row>
     <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="9" t="s">
-        <v>242</v>
+      <c r="B9" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -1534,12 +1497,12 @@
     </row>
     <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -1555,12 +1518,12 @@
     </row>
     <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -1603,7 +1566,7 @@
         <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1611,10 +1574,10 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
@@ -1622,10 +1585,10 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
@@ -1633,10 +1596,10 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1652,14 +1615,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="8" width="24.7109375" customWidth="1"/>
-    <col min="9" max="9" width="41.140625" customWidth="1"/>
+    <col min="3" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="41.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1667,31 +1630,25 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>172</v>
+        <v>149</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" t="s">
+        <v>150</v>
       </c>
       <c r="F1" t="s">
         <v>157</v>
       </c>
       <c r="G1" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1702,10 +1659,8 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1716,153 +1671,122 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" t="s">
+      <c r="G3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <v>20130828</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="J5" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>164</v>
-      </c>
-      <c r="H7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>154</v>
+      </c>
+      <c r="E8" t="s">
+        <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="10" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="15" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1872,86 +1796,82 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.28515625" style="6" customWidth="1"/>
     <col min="2" max="2" width="57.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="56.140625" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="6"/>
+    <col min="3" max="3" width="56.140625" style="6" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C3" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="B5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C6" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>36</v>
       </c>
@@ -1959,594 +1879,579 @@
         <v>37</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="178.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="C45" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="B48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="178.5" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
+      <c r="C52" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="C54" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C57" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>173</v>
+        <v>160</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2557,31 +2462,27 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="D1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/assets/framework/forms/framework/framework.xlsx
+++ b/app/config/assets/framework/forms/framework/framework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\assets\framework\forms\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0566E08F-92DA-4D96-84C2-B839032E8DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB9BB16-3AFE-4AD1-8906-03C66B11C319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="5" r:id="rId1"/>
@@ -739,9 +739,6 @@
     <t>"?" + odkSurvey.getHashString('sentinela')</t>
   </si>
   <si>
-    <t>"?" + odkSurvey.getHashString('sentinela','resultado')</t>
-  </si>
-  <si>
     <t>"?" + odkSurvey.getHashString('sentinela','consulta')</t>
   </si>
   <si>
@@ -749,6 +746,9 @@
   </si>
   <si>
     <t>framework_variant</t>
+  </si>
+  <si>
+    <t>"?" + odkSurvey.getHashString('resultado')</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -1599,7 +1599,7 @@
         <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="9" spans="1:8" s="10" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B9" s="9">
         <v>1</v>
